--- a/Result/checksun_type/模具.xlsx
+++ b/Result/checksun_type/模具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>52.82000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>52.46</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.97</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10207286.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>10441733.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>10441733.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>11354437.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>13805752.32</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>13805752.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-350711.3396960385</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10207286</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10207286.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>52.64000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.78</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>8617267.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>10670288.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>10670288</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>11115888.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>13709193.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>13709193.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-350684.620975012</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>8617267</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>8617267.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>52.6</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>49.58</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.58</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>14434524.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>11325512.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>11325512.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>11269004.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>13938314.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>13938314.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-167762.8220530096</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>14434524</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>14434524.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>52.56</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.26</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7812252.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>10609733.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>10609733.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>10716929.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>13767014.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>13767014.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-523731.9728053976</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7812252</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7812252.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>52.76000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.33</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>49.25</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>49.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>11137339.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10214252.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10214252</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>10817656.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>13861707.92</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>13861707.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-304025.4748514723</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>11137339</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>11137339.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>53.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>52.41</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>52.41</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>49.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>11350058.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>12267141.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>12267141.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>10851356.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>13826094.4</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>13826094.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-335560.317958314</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>11350058</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>11350058.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>52.76000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>52.39</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>48.91</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>48.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>11893390.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>11561489.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>11561489.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>11165019.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>13813369.2</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>13813369.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-391417.1181838587</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>11893390</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>11893390.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.36</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>48.71</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>48.71</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>10855628.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>11212496.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>11212496.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>11234627.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>13717159.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>13717159.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-515447.5071423575</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>10855628</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>10855628.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>52.46</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>48.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>5834845.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>10824126.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>10824126</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>11835375.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>13575697.54</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>13575697.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-563036.1518279854</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>5834845</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>5834845.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>48.3</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>48.3</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>21401787.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>11421060.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>11421060.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>11978537.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>13534182.66</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>13534182.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-72970.46024216898</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>21401787</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21401787.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>51.92</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>52.16</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>48.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>7821797.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>9435571.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>9435571.800000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>10925577.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>13237268.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>13237268.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1038157.170110926</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>7821797</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7821797.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>83.88</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>81.15</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>77.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>77.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>213896698.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>504772584.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>504772584.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>332966839.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>296796978.54</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>296796978.54</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>8142708.803127825</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>213896698</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>213896698.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>83.22</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>81.35</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>77.18</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>77.18000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>333409921.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>480880190.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>480880190.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>371960417.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>294937049.8</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>294937049.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>26184662.6555354</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>333409921</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>333409921.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>82.82</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>81.28</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>77.03</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>77.03</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>573541931.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>439505475.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>439505475.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>355695238.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>291760727.28</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>291760727.28</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>38218727.74270576</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>573541931</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>573541931.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>82.28</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>81.06</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>76.84</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>76.84</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>818618845.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>368965626.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>368965626.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>310112139.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>284161203.66</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>284161203.66</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>28316865.09070969</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>818618845</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>818618845.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>81.08</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>80.78</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>76.66</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>76.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>584395526.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>236650302.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>236650302.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>239077486.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>271483731.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>271483731.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-13098210.37966722</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>584395526</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>584395526.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>79.84</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>80.47</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>76.38</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>76.38</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>94434729.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>161161094.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>161161094</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>202232241.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>261484234.4</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>261484234.4</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-46699455.07378897</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>94434729</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>94434729.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>80.32</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>80.35</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>76.25</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>76.25</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>126536347.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>263040645.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>263040645.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>216492202.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>262852891.7</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>262852891.7</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-40537595.84847045</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>126536347</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>126536347.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>79.9</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>80.24</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>76.19</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>76.19</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>220842684.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>271885001.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>271885001.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>223066373.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>263858802.06</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>263858802.06</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-33726627.60342717</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>220842684</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>220842684.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>79.35999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>79.92</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>76.05</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>76.05</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>157042227.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>251258651.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>251258651.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>223487178.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>263437077.76</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>263437077.76</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-32896400.94610006</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>157042227</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>157042227.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>79.32000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>79.76</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>76.01</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>76.01000000000001</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>206949483.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>241504669.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>241504669.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>250238152.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>268014618.9</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>268014618.9</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-23699728.15184349</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>206949483</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>206949483.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>79.26</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>79.28</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>75.98</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>79.28</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>75.98</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>603832486.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>243303388.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>243303388.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>478474465.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>273726863.86</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>273726863.86</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-15062411.29748261</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>603832486</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>603832486.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>53.34</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>51.78</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>51.67</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>51.67</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2449221.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>12808622.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>12808622.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>13226048.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>5670478.74</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>5670478.74</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1904173.062620861</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2449221</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2449221.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>51.66</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>51.64</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>51.64</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>54812475.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>13716163.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>13716163.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>13106992.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>5665684.36</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>5665684.36</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>3315675.505646704</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>54812475</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>54812475.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>52.58000000000001</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>51.54</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>51.61</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>51.61</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1939839.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>4131975.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>4131975.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>7912217.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>4597832.22</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>4597832.22</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-396658.0580894761</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1939839</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1939839.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>52.12</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>51.45</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>51.59</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>51.59</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3398754.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>4125669.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>4125669.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>7829777.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>4569706.76</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>4569706.76</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-20900.07563796453</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3398754</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3398754.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>51.78000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>51.36</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>51.57</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>51.36</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>51.57</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1442823.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>13612188.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>13612188.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>7563388.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>4533015.6</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>4533015.6</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>360331.1519941222</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1442823</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1442823.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>51.5</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>6986926.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>13643474.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>13643474.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>10254232.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>4539513.64</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>4539513.64</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>1101642.257468741</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>6986926</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>6986926.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>51.18</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>51.25</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>51.54</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>51.54</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>6891535.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>12497821.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>12497821.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>10304360.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>4427999.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>4427999.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>1527302.720380027</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>6891535</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>6891535.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>51.24</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>51.55</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>51.55</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>1908310.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>11692460.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>11692460</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>9784858.5</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>4303102.64</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>4303102.64</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>2091063.034525434</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1908310</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1908310.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>51.25</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>50831348.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>11533885.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>11533885</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>9830585.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>4300279.86</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>4300279.86</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>3355671.053500108</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>50831348</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>50831348.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>51.16</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1599255.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1514589.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1514589</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4978430.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>3325504.7</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>3325504.7</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-199345.5284467889</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1599255</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1599255.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>51.14</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>51.58</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>1258661.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>6864990.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>6864990.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>4926666.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>3300804.76</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>3300804.76</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>4045.944787886925</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1258661</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1258661.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>79.64</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>83.99</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>83.05</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>83.05</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>58258727.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>81634455.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>81634455.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>115083497.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>204090725.46</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>204090725.46</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-38089682.98646478</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>58258727</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>58258727.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>79.4</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>83.04</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>83.04000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>81486955.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>95253568.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>95253568</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>120220207.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>204953686.3</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>204953686.3</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-37800491.22076954</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>81486955</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>81486955.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>79.6</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>85.24</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>83.06</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>83.06</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>56008713.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>111419359.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>111419359</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>124660268.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>205224740.4</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>205224740.4</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-38526081.29760599</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>56008713</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>56008713.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>80.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>85.6</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>83.11</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>83.11</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>136796456.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>121653884.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>121653884.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>138697684.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>207198587.04</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>207198587.04</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-35456895.43245786</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>136796456</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>136796456.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>81.75999999999999</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>83.23</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>83.23</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>75621428.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>124505003.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>124505003.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>195809999.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>206431973.26</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>206431973.26</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-38461856.10965845</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>75621428</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>75621428.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>82.78</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>86.07</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>83.28</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>126354288.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>148532539.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>148532539.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>204680045.3</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>207317223.06</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>207317223.06</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-34826552.0731715</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>126354288</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>126354288.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>84.16</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>86.39</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>83.37</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>83.37</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>162315910.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>145186847.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>145186847</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>213570329.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>220085335.38</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>220085335.38</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-33825118.73271975</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>162315910</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>162315910.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>85.05999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>86.45</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>83.58</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>83.58</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>107181340.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>137901178.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>137901178.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>217862538.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>226493478.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>226493478</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-35039490.64876297</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>107181340</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>107181340.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>85.02</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>86.29</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>83.63</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>86.29000000000001</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>83.63</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>151052050.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>155741483.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>155741483.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>226422553.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>226666785.26</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>226666785.26</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-29615621.93422604</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>151052050</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>151052050.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>85.74000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>86.51</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>83.7</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>83.7</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>195759110.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>267114996.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>267114996.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>239111235.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>227583931.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>227583931.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-25509970.48723665</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>195759110</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>195759110.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>86.28</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>86.18</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>83.75</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>86.18000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>83.75</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>109625825.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>260827551.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>260827551</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>253931033.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>228805701.34</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>228805701.34</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-23523725.90270764</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>109625825</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>109625825.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>15.16</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>16.16</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>759015.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>822662.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>822662.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>899025.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>839437.72</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>839437.72</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-27651.22974182363</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>759015</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>759015.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>15.09</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>16.2</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>16.2</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>610121.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>888460.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>888460.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>911030.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>833228.32</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>833228.3199999999</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-24939.23107736837</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>610121</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>610121.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>16.25</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>328107.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>1019582.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>1019582.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>881008.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>833631.48</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>833631.48</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-4221.331875383272</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>328107</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>328107.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>15.21</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>16.3</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1370613.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>1039667.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>1039667.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>976340.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>832143.12</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>832143.12</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>55742.21455157339</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1370613</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1370613.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>15.29</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>16.35</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1045458.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>969620.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>969620.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>895996.7</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>815201.94</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>815201.9399999999</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>27716.55892752646</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1045458</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1045458.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>15.34</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>16.4</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>1088003.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>975388.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>975388.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>889500.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>803125.26</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>803125.26</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>21528.0666457623</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>1088003</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>1088003.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>15.38</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>16.45</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>1265731.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>933601.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>933601</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>848828.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>789392.84</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>789392.84</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>7360.111005893559</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>1265731</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>1265731.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>15.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>16.49</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>16.49</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>428532.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>742433.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>742433.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>764703.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>770458.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>770458</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-32184.97244412953</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>428532</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>428532.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>15.43</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>16.53</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>1020378.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>913013.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>913013.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>789901.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>831542.84</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>831542.84</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>2171.407357413555</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>1020378</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>1020378.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>15.75</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>16.58</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1074300.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>822373.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>822373</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>741812.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>839169.14</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>839169.14</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-12237.67176028958</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1074300</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1074300.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>15.51</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>15.8</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>16.62</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>16.62</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>879064.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>803612.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>803612.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>728036.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>823720.16</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>823720.16</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-38162.36793699802</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>879064</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>879064.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>20.02</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>19.78</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>26219629.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>16889576.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>16889576</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>17236189.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>20277790.28</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>20277790.28</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-302881.9023336619</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>26219629</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>26219629.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>19.94</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>19.94</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>17532722.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>14859100.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>14859100</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>16642108.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>20371841.18</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>20371841.18</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-1128834.726736229</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>17532722</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>17532722.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>19.84</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>19.95</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>11740057.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>16014559.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>16014559.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>16278001.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>20292426.12</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>20292426.12</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1337711.771356456</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>11740057</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>11740057.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>19.82</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>19.96</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>19.96</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>18789662.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>18102005.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>18102005</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>17635266.7</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>20278770.0</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>20278770</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-967689.4504083358</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>18789662</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>18789662.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>10165810.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>17346115.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>17346115.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>24061820.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>20181907.52</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>20181907.52</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-1159840.618682154</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>10165810</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>10165810.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>19.94</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>19.97</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>19.97</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>16067249.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>17582802.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>17582802.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>24285645.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>20299032.42</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>20299032.42</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-468935.2655489594</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>16067249</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>16067249.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>19.99</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>23310018.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>18425116.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>18425116.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>24110880.8</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>20453854.52</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>20453854.52</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-97476.96587479487</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>23310018</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>23310018.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>20.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>19.62</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>20</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>22177286.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>16541443.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>16541443.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>23454311.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>20348159.38</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>20348159.38</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-339351.8961304575</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>22177286</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>22177286.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>20.13</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>20</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>15010216.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>17168528.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>17168528.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>22516228.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>20143353.8</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>20143353.8</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-551403.6573481709</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>15010216</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>15010216.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>20.01</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>11349244.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>30777524.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>30777524.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>22335947.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>20370385.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>20370385.8</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-66741.39989675581</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>11349244</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>11349244.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>20.05</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>19.55</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>20.02</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>20278820.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>30988489.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>30988489</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>22686745.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>20671912.34</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>20671912.34</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>1020263.875030149</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>20278820</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>20278820.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
